--- a/tools/importer/reports/import-customer-segments.report.xlsx
+++ b/tools/importer/reports/import-customer-segments.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="99">
   <si>
     <t>_reportFile</t>
   </si>
@@ -151,7 +151,28 @@
     <t>tangent-energy/en-us</t>
   </si>
   <si>
-    <t>2026-08-22T12:54:22.410Z</t>
+    <t>2026-08-24T08:03:38.972Z</t>
+  </si>
+  <si>
+    <t>turner-powertrain/en-us.report.json</t>
+  </si>
+  <si>
+    <t>["page-hero","cards-promo","cards-feature","columns-media","columns-media"]</t>
+  </si>
+  <si>
+    <t>turner-powertrain/en-us</t>
+  </si>
+  <si>
+    <t>turner-home</t>
+  </si>
+  <si>
+    <t>2026-08-24T06:45:38.864Z</t>
+  </si>
+  <si>
+    <t>Turner | Turner Power Train</t>
+  </si>
+  <si>
+    <t>https://www.turner-powertrain.com/en_US.html</t>
   </si>
   <si>
     <t>tangent-energy/en-us/about-us.report.json</t>
@@ -160,7 +181,7 @@
     <t>tangent-energy/en-us/about-us</t>
   </si>
   <si>
-    <t>2026-08-22T12:54:28.865Z</t>
+    <t>2026-08-24T08:03:48.169Z</t>
   </si>
   <si>
     <t>tangent-energy/en-us/customer-segments.report.json</t>
@@ -169,7 +190,7 @@
     <t>tangent-energy/en-us/customer-segments</t>
   </si>
   <si>
-    <t>2026-08-22T12:54:44.951Z</t>
+    <t>2026-08-24T08:04:08.234Z</t>
   </si>
   <si>
     <t>tangent-energy/en-us/meet-the-team.report.json</t>
@@ -178,7 +199,115 @@
     <t>tangent-energy/en-us/meet-the-team</t>
   </si>
   <si>
-    <t>2026-08-22T12:54:36.480Z</t>
+    <t>2026-08-24T08:03:58.674Z</t>
+  </si>
+  <si>
+    <t>tangent-energy/en-us/tangent-amp.report.json</t>
+  </si>
+  <si>
+    <t>tangent-energy/en-us/tangent-amp</t>
+  </si>
+  <si>
+    <t>2026-08-22T12:54:52.259Z</t>
+  </si>
+  <si>
+    <t>turner-powertrain/en-us/about-us.report.json</t>
+  </si>
+  <si>
+    <t>["page-hero","timeline"]</t>
+  </si>
+  <si>
+    <t>turner-powertrain/en-us/about-us</t>
+  </si>
+  <si>
+    <t>turner-about</t>
+  </si>
+  <si>
+    <t>2026-08-24T05:41:54.017Z</t>
+  </si>
+  <si>
+    <t>About Us | Turner Power Train</t>
+  </si>
+  <si>
+    <t>https://www.turner-powertrain.com/en_US/about-us.html</t>
+  </si>
+  <si>
+    <t>turner-powertrain/en-us/knowledge-hub.report.json</t>
+  </si>
+  <si>
+    <t>["page-hero","resource-cards","columns-media"]</t>
+  </si>
+  <si>
+    <t>turner-powertrain/en-us/knowledge-hub</t>
+  </si>
+  <si>
+    <t>turner-knowledge-hub</t>
+  </si>
+  <si>
+    <t>2026-08-24T06:45:48.248Z</t>
+  </si>
+  <si>
+    <t>Knowledge Hub | Turner Power Train</t>
+  </si>
+  <si>
+    <t>https://www.turner-powertrain.com/en_US/knowledge-hub.html</t>
+  </si>
+  <si>
+    <t>turner-powertrain/en-us/products.report.json</t>
+  </si>
+  <si>
+    <t>["resource-cards"]</t>
+  </si>
+  <si>
+    <t>turner-powertrain/en-us/products</t>
+  </si>
+  <si>
+    <t>turner-products</t>
+  </si>
+  <si>
+    <t>2026-08-24T05:46:35.547Z</t>
+  </si>
+  <si>
+    <t>Products | Turner Power Train</t>
+  </si>
+  <si>
+    <t>https://www.turner-powertrain.com/en_US/products.html</t>
+  </si>
+  <si>
+    <t>turner-powertrain/en-us/products/c90.report.json</t>
+  </si>
+  <si>
+    <t>["page-hero","tabs","tabs","columns-media","columns-media"]</t>
+  </si>
+  <si>
+    <t>turner-powertrain/en-us/products/c90</t>
+  </si>
+  <si>
+    <t>turner-product-detail</t>
+  </si>
+  <si>
+    <t>2026-08-24T06:43:57.114Z</t>
+  </si>
+  <si>
+    <t>C90 | Turner Power Train</t>
+  </si>
+  <si>
+    <t>https://www.turner-powertrain.com/en_US/products/c90.html</t>
+  </si>
+  <si>
+    <t>turner-powertrain/en-us/products/pg145.report.json</t>
+  </si>
+  <si>
+    <t>turner-powertrain/en-us/products/pg145</t>
+  </si>
+  <si>
+    <t>2026-08-24T06:44:01.672Z</t>
+  </si>
+  <si>
+    <t>PG145 | Turner Power Train</t>
+  </si>
+  <si>
+    <t>https://www.turner-powertrain.com/en_US/products/pg145.html</t>
   </si>
 </sst>
 </file>
@@ -567,13 +696,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="2" width="49" customWidth="1"/>
+    <col min="1" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="8" width="50" customWidth="1"/>
   </cols>
@@ -765,77 +893,259 @@
         <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G8" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="H8" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G9" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="H9" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
         <v>31</v>
       </c>
-      <c r="C10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="C11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
         <v>33</v>
       </c>
-      <c r="F10" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="F11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" t="s">
         <v>35</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H11" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" t="s">
+        <v>42</v>
+      </c>
+      <c r="H12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" t="s">
+        <v>71</v>
+      </c>
+      <c r="H13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" t="s">
+        <v>78</v>
+      </c>
+      <c r="H14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>83</v>
+      </c>
+      <c r="F15" t="s">
+        <v>84</v>
+      </c>
+      <c r="G15" t="s">
+        <v>85</v>
+      </c>
+      <c r="H15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>90</v>
+      </c>
+      <c r="F16" t="s">
+        <v>91</v>
+      </c>
+      <c r="G16" t="s">
+        <v>92</v>
+      </c>
+      <c r="H16" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>90</v>
+      </c>
+      <c r="F17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G17" t="s">
+        <v>97</v>
+      </c>
+      <c r="H17" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
